--- a/Protein_data_PIAU.xlsx
+++ b/Protein_data_PIAU.xlsx
@@ -19,6 +19,32 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+  <si>
+    <t xml:space="preserve">HTR8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endoglina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlGF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
@@ -29,6 +55,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -88,9 +115,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -216,9 +251,168 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>0.440473140001595</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0.702167773628005</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0.626049086309676</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0.382993815413475</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0.33883515573943</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.320601873816232</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0.466185562474046</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>2.18236318257081</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>0.991034262778767</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.909696608793041</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0.760704496303173</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0.66278693553035</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0.326801980377375</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>2.43056627885722</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>2.53627412759976</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>1.61818188574324</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>1.56849259721964</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1.38624025588545</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>1.27811804298205</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.862050620663991</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>2.3343628638832</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>1.98595049613943</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>2.04081100708251</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>1.24452897758071</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.999368212768833</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0.888290541864966</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0.635943790535939</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>1.57903954960429</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1.68109023238544</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>1.68169134863159</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F2:I2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
